--- a/inputs/AddictO_Organisation_Defs.xlsx
+++ b/inputs/AddictO_Organisation_Defs.xlsx
@@ -463,97 +463,97 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Parent</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Synonyms</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Sub-ontology</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Why fuzzy</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'has role'</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>REL 'has part'</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Curator note</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>Informal definition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Parent</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>E-CigO</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>To be reviewed by</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Examples of usage</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Definition source</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Sub-ontology</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Curator</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>BFO entity</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'has role'</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>REL 'has part'</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Curator note</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Synonyms</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Curation status</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Fuzzy set</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Comment</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Examples of usage</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>E-CigO</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Why fuzzy</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Curator</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Curation status</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>To be reviewed by</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
@@ -580,14 +580,10 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>A commercial organisation that deals with nicotine products or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
           <t>commercial organisation</t>
         </is>
       </c>
+      <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="n"/>
       <c r="H2" s="2" t="inlineStr">
@@ -595,32 +591,36 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="n"/>
-      <c r="O2" s="2" t="n">
-        <v>0</v>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>A commercial organisation that deals with nicotine products or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="P2" s="2" t="n"/>
       <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="R2" s="2" t="n"/>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="n"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V2" s="2" t="n"/>
+      <c r="V2" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" s="2" t="n"/>
     </row>
     <row r="3">
@@ -639,10 +639,14 @@
           <t>A charity that provides funding for research, prevention, treatment or care relating to alcohol use.</t>
         </is>
       </c>
-      <c r="D3" s="3" t="n"/>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>organisation</t>
+        </is>
+      </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>organisation</t>
+          <t xml:space="preserve">alcohol harm prevention organisation </t>
         </is>
       </c>
       <c r="F3" s="3" t="n"/>
@@ -652,20 +656,12 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
       <c r="L3" s="3" t="n"/>
       <c r="M3" s="3" t="n"/>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">alcohol harm prevention organisation </t>
-        </is>
-      </c>
+      <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
           <t>0</t>
@@ -673,15 +669,15 @@
       </c>
       <c r="P3" s="3" t="n"/>
       <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="n"/>
+      <c r="R3" s="3" t="n"/>
+      <c r="S3" s="3" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U3" s="3" t="inlineStr">
@@ -689,7 +685,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V3" s="3" t="n"/>
+      <c r="V3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W3" s="3" t="n"/>
     </row>
     <row r="4">
@@ -708,12 +708,12 @@
           <t>An industry that is realised in the manufacture and sale of alcoholic beverages.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n"/>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
+      <c r="E4" s="4" t="n"/>
       <c r="F4" s="4" t="n"/>
       <c r="G4" s="4" t="n"/>
       <c r="H4" s="4" t="inlineStr">
@@ -721,11 +721,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
       <c r="K4" s="4" t="n"/>
       <c r="L4" s="4" t="n"/>
@@ -738,15 +734,15 @@
       </c>
       <c r="P4" s="4" t="n"/>
       <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="4" t="n"/>
+      <c r="R4" s="4" t="n"/>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T4" s="4" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="U4" s="4" t="inlineStr">
@@ -754,7 +750,11 @@
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V4" s="4" t="n"/>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W4" s="4" t="n"/>
     </row>
     <row r="5">
@@ -773,12 +773,12 @@
           <t>An organisation that undertakes assays for presence or amounts of chemicals in specimens</t>
         </is>
       </c>
-      <c r="D5" s="3" t="n"/>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E5" s="3" t="n"/>
       <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="inlineStr">
@@ -786,11 +786,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role </t>
-        </is>
-      </c>
+      <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
       <c r="L5" s="3" t="n"/>
@@ -803,15 +799,15 @@
       </c>
       <c r="P5" s="3" t="n"/>
       <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" s="3" t="n"/>
+      <c r="R5" s="3" t="n"/>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t xml:space="preserve">Role </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
@@ -819,7 +815,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V5" s="3" t="n"/>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W5" s="3" t="n"/>
     </row>
     <row r="6">
@@ -838,10 +838,14 @@
           <t>A charity that provides funding for cancer-related research, prevention, treatment or care.</t>
         </is>
       </c>
-      <c r="D6" s="3" t="n"/>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">organisation </t>
+        </is>
+      </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">organisation </t>
+          <t xml:space="preserve">cancer prevention organisation </t>
         </is>
       </c>
       <c r="F6" s="3" t="n"/>
@@ -851,34 +855,26 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role </t>
-        </is>
-      </c>
+      <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
       <c r="L6" s="3" t="n"/>
       <c r="M6" s="3" t="n"/>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cancer prevention organisation </t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="N6" s="3" t="n"/>
+      <c r="O6" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="P6" s="3" t="n"/>
       <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="3" t="n"/>
+      <c r="R6" s="3" t="n"/>
+      <c r="S6" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t xml:space="preserve">Role </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
@@ -886,7 +882,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V6" s="3" t="n"/>
+      <c r="V6" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W6" s="3" t="n"/>
     </row>
     <row r="7">
@@ -905,12 +905,12 @@
           <t xml:space="preserve">An organisation that is engaged in the growth, manufacture, preparation for sale, shipment, advertisement, or distribution of cannabis products. </t>
         </is>
       </c>
-      <c r="D7" s="3" t="n"/>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E7" s="3" t="n"/>
       <c r="F7" s="3" t="n"/>
       <c r="G7" s="3" t="n"/>
       <c r="H7" s="3" t="inlineStr">
@@ -918,11 +918,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role </t>
-        </is>
-      </c>
+      <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
       <c r="L7" s="3" t="n"/>
@@ -935,15 +931,15 @@
       </c>
       <c r="P7" s="3" t="n"/>
       <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="3" t="n"/>
+      <c r="R7" s="3" t="n"/>
+      <c r="S7" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH; KS</t>
+        </is>
+      </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>SC; JH; KS</t>
+          <t xml:space="preserve">Role </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
@@ -951,7 +947,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V7" s="3" t="n"/>
+      <c r="V7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W7" s="3" t="n"/>
     </row>
     <row r="8">
@@ -970,12 +970,12 @@
           <t>An industry that is realised in the manufacture and sale of cannabis.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
+      <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="n"/>
       <c r="H8" s="2" t="inlineStr">
@@ -983,11 +983,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="I8" s="2" t="n"/>
       <c r="J8" s="2" t="n"/>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="n"/>
@@ -1000,15 +996,15 @@
       </c>
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="n"/>
+      <c r="R8" s="2" t="n"/>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1016,7 +1012,11 @@
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V8" s="2" t="n"/>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W8" s="2" t="n"/>
     </row>
     <row r="9">
@@ -1035,12 +1035,12 @@
           <t xml:space="preserve">A cannabis retailer that has a physical outlet. </t>
         </is>
       </c>
-      <c r="D9" s="3" t="n"/>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>cannabis retailer</t>
         </is>
       </c>
+      <c r="E9" s="3" t="n"/>
       <c r="F9" s="3" t="n"/>
       <c r="G9" s="3" t="n"/>
       <c r="H9" s="3" t="inlineStr">
@@ -1048,11 +1048,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role </t>
-        </is>
-      </c>
+      <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
       <c r="L9" s="3" t="n"/>
@@ -1065,15 +1061,15 @@
       </c>
       <c r="P9" s="3" t="n"/>
       <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="n"/>
+      <c r="R9" s="3" t="n"/>
+      <c r="S9" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t xml:space="preserve">Role </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
@@ -1081,7 +1077,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V9" s="3" t="n"/>
+      <c r="V9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W9" s="3" t="n"/>
     </row>
     <row r="10">
@@ -1100,12 +1100,12 @@
           <t xml:space="preserve">A cannabis company that predominantly sells cannabis products and related merchandise. </t>
         </is>
       </c>
-      <c r="D10" s="3" t="n"/>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cannabis company </t>
         </is>
       </c>
+      <c r="E10" s="3" t="n"/>
       <c r="F10" s="3" t="n"/>
       <c r="G10" s="3" t="n"/>
       <c r="H10" s="3" t="inlineStr">
@@ -1113,11 +1113,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role </t>
-        </is>
-      </c>
+      <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
       <c r="L10" s="3" t="n"/>
@@ -1130,15 +1126,15 @@
       </c>
       <c r="P10" s="3" t="n"/>
       <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="n"/>
+      <c r="R10" s="3" t="n"/>
+      <c r="S10" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t xml:space="preserve">Role </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
@@ -1146,7 +1142,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V10" s="3" t="n"/>
+      <c r="V10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W10" s="3" t="n"/>
     </row>
     <row r="11">
@@ -1165,12 +1165,12 @@
           <t xml:space="preserve">An organisation that raises and distributes funds for charitable purposes. </t>
         </is>
       </c>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E11" s="2" t="n"/>
       <c r="F11" s="2" t="n"/>
       <c r="G11" s="2" t="n"/>
       <c r="H11" s="2" t="inlineStr">
@@ -1178,30 +1178,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I11" s="2" t="n"/>
       <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
       <c r="M11" s="2" t="n"/>
       <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
+      <c r="O11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>RW; CN</t>
+        </is>
+      </c>
       <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S11" s="2" t="n"/>
+      <c r="R11" s="2" t="n"/>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W11" s="2" t="n"/>
@@ -1234,14 +1234,10 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>An organisation whose main goal is making money by selling products or services.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n"/>
       <c r="G12" s="2" t="n"/>
       <c r="H12" s="2" t="inlineStr">
@@ -1249,32 +1245,36 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
-      <c r="O12" s="2" t="n">
-        <v>0</v>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>An organisation whose main goal is making money by selling products or services.</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="P12" s="2" t="n"/>
       <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="R12" s="2" t="n"/>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="n"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V12" s="2" t="n"/>
+      <c r="V12" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W12" s="2" t="n"/>
     </row>
     <row r="13">
@@ -1295,14 +1295,10 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>A commercial organisation that deals with e-cigarettes or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
           <t>commercial organisation</t>
         </is>
       </c>
+      <c r="E13" s="2" t="n"/>
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="n"/>
       <c r="H13" s="2" t="inlineStr">
@@ -1310,32 +1306,36 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
       <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
-      <c r="O13" s="2" t="n">
-        <v>0</v>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>A commercial organisation that deals with e-cigarettes or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="P13" s="2" t="n"/>
       <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="R13" s="2" t="n"/>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="n"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V13" s="2" t="n"/>
+      <c r="V13" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W13" s="2" t="n"/>
     </row>
     <row r="14">
@@ -1354,10 +1354,14 @@
           <t>An industry that is realised in the manufacture and sale of e-cigarettes, e-cigarette components and e-liquid.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>industry</t>
+        </is>
+      </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>industry</t>
+          <t>E-Cig industry</t>
         </is>
       </c>
       <c r="F14" s="4" t="n"/>
@@ -1367,38 +1371,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I14" s="4" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="I14" s="4" t="n"/>
       <c r="J14" s="4" t="n"/>
       <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="inlineStr">
+      <c r="L14" s="4" t="n"/>
+      <c r="M14" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">I have added here promotion of - this sets industry apart from manufactureres of but also includes these types of company. </t>
         </is>
       </c>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>E-Cig industry</t>
-        </is>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="N14" s="4" t="n"/>
+      <c r="O14" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="P14" s="4" t="n"/>
       <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S14" s="4" t="n"/>
+      <c r="R14" s="4" t="n"/>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
@@ -1406,7 +1402,11 @@
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V14" s="4" t="n"/>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W14" s="4" t="n"/>
     </row>
     <row r="15">
@@ -1425,10 +1425,14 @@
           <t>A e-cigarette company that predominantly sells e-cigarettes, e-cigarette components or e-liquid to consumers.</t>
         </is>
       </c>
-      <c r="D15" s="3" t="n"/>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>e-cigarette company</t>
+        </is>
+      </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>e-cigarette company</t>
+          <t>E-Cig shop; E-cig Industry; E-Cig merchant; vape shop; vape retailer</t>
         </is>
       </c>
       <c r="F15" s="3" t="n"/>
@@ -1438,34 +1442,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
+      <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
       <c r="L15" s="3" t="n"/>
       <c r="M15" s="3" t="n"/>
-      <c r="N15" s="3" t="inlineStr">
-        <is>
-          <t>E-Cig shop; E-cig Industry; E-Cig merchant; vape shop; vape retailer</t>
-        </is>
-      </c>
-      <c r="O15" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
+      <c r="N15" s="3" t="n"/>
+      <c r="O15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S15" s="3" t="n"/>
+      <c r="R15" s="3" t="n"/>
+      <c r="S15" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH</t>
+        </is>
+      </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t>SC; JH</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
@@ -1475,7 +1475,7 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W15" s="3" t="n"/>
@@ -1496,12 +1496,12 @@
           <t>An e-cigarette shop is an e-cigarette retailer that has a physical outlet.</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>e-cigarette retailer</t>
         </is>
       </c>
+      <c r="E16" s="3" t="n"/>
       <c r="F16" s="3" t="n"/>
       <c r="G16" s="3" t="n"/>
       <c r="H16" s="3" t="inlineStr">
@@ -1509,30 +1509,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
+      <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
       <c r="L16" s="3" t="n"/>
       <c r="M16" s="3" t="n"/>
       <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+      <c r="O16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S16" s="3" t="n"/>
+      <c r="R16" s="3" t="n"/>
+      <c r="S16" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH</t>
+        </is>
+      </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t>SC; JH</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W16" s="3" t="n"/>
@@ -1563,12 +1563,12 @@
           <t>An e-cigarette organisation that is engaged in the growth, manufacture, preparation for sale, shipment, advertisement, or distribution of e-liquid.</t>
         </is>
       </c>
-      <c r="D17" s="3" t="n"/>
-      <c r="E17" s="3" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>e-cigarette organisation</t>
         </is>
       </c>
+      <c r="E17" s="3" t="n"/>
       <c r="F17" s="3" t="n"/>
       <c r="G17" s="3" t="n"/>
       <c r="H17" s="3" t="inlineStr">
@@ -1576,30 +1576,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
+      <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
       <c r="L17" s="3" t="n"/>
       <c r="M17" s="3" t="n"/>
       <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+      <c r="O17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S17" s="3" t="n"/>
+      <c r="R17" s="3" t="n"/>
+      <c r="S17" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH</t>
+        </is>
+      </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t>SC; JH</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W17" s="3" t="n"/>
@@ -1630,12 +1630,12 @@
           <t>An industry that is realised in the processes of facilitating and managing the wagering of money or valuables.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n"/>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
+      <c r="E18" s="2" t="n"/>
       <c r="F18" s="2" t="n"/>
       <c r="G18" s="2" t="n"/>
       <c r="H18" s="2" t="inlineStr">
@@ -1643,11 +1643,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="I18" s="2" t="n"/>
       <c r="J18" s="2" t="n"/>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="n"/>
@@ -1660,15 +1656,15 @@
       </c>
       <c r="P18" s="2" t="n"/>
       <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="n"/>
+      <c r="R18" s="2" t="n"/>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -1676,7 +1672,11 @@
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V18" s="2" t="n"/>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W18" s="2" t="n"/>
     </row>
     <row r="19">
@@ -1695,47 +1695,43 @@
           <t>A governmental organisation set up for a purpose.</t>
         </is>
       </c>
-      <c r="D19" s="3" t="n"/>
-      <c r="E19" s="3" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">organisation </t>
         </is>
       </c>
-      <c r="F19" s="3" t="n"/>
+      <c r="E19" s="3" t="n"/>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>These are set up for purposes such as management of resources, financial oversight of industries, or national security issues. These organizations are typically created by legislative action, but may initially be set up by presidential order as well. The directors of these agencies are typically selected by Presidential appointment</t>
+        </is>
+      </c>
       <c r="G19" s="3" t="n"/>
       <c r="H19" s="3" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
+      <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
       <c r="L19" s="3" t="n"/>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>These are set up for purposes such as management of resources, financial oversight of industries, or national security issues. These organizations are typically created by legislative action, but may initially be set up by presidential order as well. The directors of these agencies are typically selected by Presidential appointment</t>
-        </is>
-      </c>
+      <c r="O19" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P19" s="3" t="n"/>
       <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S19" s="3" t="n"/>
+      <c r="R19" s="3" t="n"/>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
@@ -1743,7 +1739,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V19" s="3" t="n"/>
+      <c r="V19" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W19" s="3" t="n"/>
     </row>
     <row r="20">
@@ -1764,14 +1764,10 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>An organisation that provides products or services that are used for purposes of improving health or reducing ill-health.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E20" s="2" t="n"/>
       <c r="F20" s="2" t="n"/>
       <c r="G20" s="2" t="n"/>
       <c r="H20" s="2" t="inlineStr">
@@ -1779,32 +1775,36 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="n"/>
-      <c r="O20" s="2" t="n">
-        <v>0</v>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>An organisation that provides products or services that are used for purposes of improving health or reducing ill-health.</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="P20" s="2" t="n"/>
       <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="R20" s="2" t="n"/>
       <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="n"/>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V20" s="2" t="n"/>
+      <c r="V20" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W20" s="2" t="n"/>
     </row>
     <row r="21">
@@ -1823,12 +1823,12 @@
           <t>An organisation that provides healthcare.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E21" s="2" t="n"/>
       <c r="F21" s="2" t="n"/>
       <c r="G21" s="2" t="n"/>
       <c r="H21" s="2" t="inlineStr">
@@ -1836,11 +1836,7 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I21" s="2" t="n"/>
       <c r="J21" s="2" t="n"/>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
@@ -1848,20 +1844,20 @@
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P21" s="2" t="n"/>
       <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="n"/>
+      <c r="R21" s="2" t="n"/>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -1869,7 +1865,11 @@
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V21" s="2" t="n"/>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W21" s="2" t="n"/>
     </row>
     <row r="22">
@@ -1888,51 +1888,51 @@
           <t xml:space="preserve">An e-cigarette company that has no commercial or financial association with a tobacco company. </t>
         </is>
       </c>
-      <c r="D22" s="3" t="n"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>e-cigarette company</t>
+        </is>
+      </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>e-cigarette company</t>
-        </is>
-      </c>
-      <c r="F22" s="3" t="n"/>
+          <t xml:space="preserve">Independent vape company; Independent vape business; vape company </t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>(Note: This is intended to include ownership, investment or sharing of resources.)</t>
+        </is>
+      </c>
       <c r="G22" s="3" t="n"/>
       <c r="H22" s="3" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
+      <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
       <c r="L22" s="3" t="n"/>
       <c r="M22" s="3" t="n"/>
-      <c r="N22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Independent vape company; Independent vape business; vape company </t>
-        </is>
-      </c>
-      <c r="O22" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="N22" s="3" t="n"/>
+      <c r="O22" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>(Note: This is intended to include ownership, investment or sharing of resources.)</t>
+          <t>RW</t>
         </is>
       </c>
       <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" s="3" t="n"/>
+      <c r="R22" s="3" t="n"/>
+      <c r="S22" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>Role</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W22" s="3" t="n"/>
@@ -1963,47 +1963,47 @@
           <t>A realizable entity that inheres in a collection of organisations, people, equipment and resources and is realised in processes of production, distribution or service provision, and is characterised by a common purpose or set of related economic activities.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
-          <t>claude.ai</t>
-        </is>
-      </c>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
       <c r="G23" s="4" t="n"/>
       <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="I23" s="4" t="n"/>
       <c r="J23" s="4" t="n"/>
       <c r="K23" s="4" t="n"/>
       <c r="L23" s="4" t="n"/>
       <c r="M23" s="4" t="n"/>
       <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P23" s="4" t="n"/>
+      <c r="O23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S23" s="4" t="n"/>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>claude.ai</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>JH; SC; RW</t>
+        </is>
+      </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>JH; SC; RW</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W23" s="4" t="n"/>
@@ -2034,12 +2034,12 @@
           <t>A process undertaken by an organisation with the aim of increasing use of a product or service.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
+      <c r="E24" s="4" t="n"/>
       <c r="F24" s="4" t="n"/>
       <c r="G24" s="4" t="n"/>
       <c r="H24" s="4" t="inlineStr">
@@ -2047,30 +2047,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I24" s="4" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
+      <c r="I24" s="4" t="n"/>
       <c r="J24" s="4" t="n"/>
       <c r="K24" s="4" t="n"/>
       <c r="L24" s="4" t="n"/>
       <c r="M24" s="4" t="n"/>
       <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P24" s="4" t="n"/>
+      <c r="O24" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S24" s="4" t="n"/>
+      <c r="R24" s="4" t="n"/>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>process</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W24" s="4" t="n"/>
@@ -2101,12 +2101,12 @@
           <t xml:space="preserve">An organisation which is involved in the prevention, diagnosis, treatment and care of people. </t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
-      <c r="E25" s="3" t="inlineStr">
+      <c r="D25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">organisation </t>
         </is>
       </c>
+      <c r="E25" s="3" t="n"/>
       <c r="F25" s="3" t="n"/>
       <c r="G25" s="3" t="n"/>
       <c r="H25" s="3" t="inlineStr">
@@ -2114,30 +2114,26 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Role </t>
-        </is>
-      </c>
+      <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n"/>
       <c r="L25" s="3" t="n"/>
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O25" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="P25" s="3" t="n"/>
       <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S25" s="3" t="n"/>
+      <c r="R25" s="3" t="n"/>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t xml:space="preserve">Role </t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
@@ -2145,7 +2141,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V25" s="3" t="n"/>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W25" s="3" t="n"/>
     </row>
     <row r="26">
@@ -2164,28 +2164,20 @@
           <t>An organization dedicated to furthering a particular social cause or advocating for a shared point of view. In economic terms, it is an organization that uses its surplus of the revenues to further achieve its ultimate objective, rather than distributing its income to the organization's shareholders, leaders, or members.</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
-      <c r="E26" s="3" t="inlineStr">
+      <c r="D26" s="3" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="F26" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/GSSO_004615</t>
-        </is>
-      </c>
+      <c r="E26" s="3" t="n"/>
+      <c r="F26" s="3" t="n"/>
       <c r="G26" s="3" t="n"/>
       <c r="H26" s="3" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="n"/>
       <c r="L26" s="3" t="n"/>
@@ -2193,20 +2185,24 @@
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>true</t>
         </is>
       </c>
       <c r="P26" s="3" t="n"/>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="n"/>
+          <t>http://purl.obolibrary.org/obo/GSSO_004615</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -2214,7 +2210,11 @@
           <t>Pre-proposed</t>
         </is>
       </c>
-      <c r="V26" s="3" t="n"/>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W26" s="3" t="n"/>
     </row>
     <row r="27">
@@ -2233,52 +2233,52 @@
           <t>A material entity which can play roles, has members, and has a set of organization rules. Members of organizations are either organizations themselves or individual people. Members can bear specific organization member roles that are determined in the organization rules. The organization rules also determine how decisions are made on behalf of the organization by the organization members.</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>The definition from OBI has been slightly changed to refer to 'material entity' rather than 'continuant entity'</t>
+        </is>
+      </c>
+      <c r="O27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>OBI:0000245</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>OBI:0000245</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>The definition from OBI has been slightly changed to refer to 'material entity' rather than 'continuant entity'</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>false</t>
-        </is>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>External</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2298,12 @@
           <t>An aggregate of organisations.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>object aggregate</t>
         </is>
       </c>
+      <c r="E28" s="5" t="n"/>
       <c r="F28" s="5" t="n"/>
       <c r="G28" s="5" t="n"/>
       <c r="H28" s="5" t="inlineStr">
@@ -2324,23 +2324,23 @@
       </c>
       <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="n"/>
-      <c r="R28" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S28" s="5" t="n"/>
-      <c r="T28" s="5" t="inlineStr">
+      <c r="R28" s="5" t="n"/>
+      <c r="S28" s="5" t="inlineStr">
         <is>
           <t>JH; RW</t>
         </is>
       </c>
+      <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="V28" s="5" t="n"/>
+      <c r="V28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W28" s="5" t="n"/>
     </row>
     <row r="29">
@@ -2361,14 +2361,10 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>A commercial organisation that deals with pharmaceutical products or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
           <t>commercial organisation</t>
         </is>
       </c>
+      <c r="E29" s="2" t="n"/>
       <c r="F29" s="2" t="n"/>
       <c r="G29" s="2" t="n"/>
       <c r="H29" s="2" t="inlineStr">
@@ -2376,32 +2372,36 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="n"/>
-      <c r="O29" s="2" t="n">
-        <v>0</v>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>A commercial organisation that deals with pharmaceutical products or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="P29" s="2" t="n"/>
       <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="R29" s="2" t="n"/>
       <c r="S29" s="2" t="n"/>
-      <c r="T29" s="2" t="n"/>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V29" s="2" t="n"/>
+      <c r="V29" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W29" s="2" t="n"/>
     </row>
     <row r="30">
@@ -2422,14 +2422,10 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>An organisation that makes or provides products or services that people use for enjoyment, entertainment, or leisure activities.</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E30" s="2" t="n"/>
       <c r="F30" s="2" t="n"/>
       <c r="G30" s="2" t="n"/>
       <c r="H30" s="2" t="inlineStr">
@@ -2437,32 +2433,36 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="n"/>
-      <c r="O30" s="2" t="n">
-        <v>0</v>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>An organisation that makes or provides products or services that people use for enjoyment, entertainment, or leisure activities.</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="P30" s="2" t="n"/>
       <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="b">
-        <v>1</v>
-      </c>
+      <c r="R30" s="2" t="n"/>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="n"/>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V30" s="2" t="n"/>
+      <c r="V30" s="2" t="n">
+        <v>0</v>
+      </c>
       <c r="W30" s="2" t="n"/>
     </row>
     <row r="31">
@@ -2481,47 +2481,43 @@
           <t>An organization that has responsibility over or for the legislation (acts and regulations) for a given sector of the government.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OBI_0000450</t>
-        </is>
-      </c>
+      <c r="E31" s="2" t="n"/>
+      <c r="F31" s="2" t="n"/>
       <c r="G31" s="2" t="n"/>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I31" s="2" t="n"/>
       <c r="J31" s="2" t="n"/>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="2" t="n"/>
       <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="O31" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="P31" s="2" t="n"/>
       <c r="Q31" s="2" t="n"/>
-      <c r="R31" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S31" s="2" t="n"/>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OBI_0000450</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>SC; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -2529,7 +2525,11 @@
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V31" s="2" t="n"/>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W31" s="2" t="n"/>
     </row>
     <row r="32">
@@ -2548,10 +2548,14 @@
           <t>An organization that provides funding for research.</t>
         </is>
       </c>
-      <c r="D32" s="2" t="n"/>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>organisation</t>
+        </is>
+      </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>organisation</t>
+          <t>funder</t>
         </is>
       </c>
       <c r="F32" s="2" t="n"/>
@@ -2561,34 +2565,26 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I32" s="2" t="n"/>
       <c r="J32" s="2" t="n"/>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="inlineStr">
-        <is>
-          <t>funder</t>
-        </is>
-      </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+      <c r="N32" s="2" t="n"/>
+      <c r="O32" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="P32" s="2" t="n"/>
       <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S32" s="2" t="n"/>
+      <c r="R32" s="2" t="n"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>SC; KS; RW</t>
+        </is>
+      </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>SC; KS; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -2596,7 +2592,11 @@
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V32" s="2" t="n"/>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="W32" s="2" t="n"/>
     </row>
     <row r="33">
@@ -2615,47 +2615,47 @@
           <t>An organisation formed with a goal to have its members conduct investigations.</t>
         </is>
       </c>
-      <c r="D33" s="3" t="n"/>
-      <c r="E33" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">organisation </t>
         </is>
       </c>
-      <c r="F33" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OBI_0000828</t>
-        </is>
-      </c>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n"/>
       <c r="G33" s="3" t="n"/>
       <c r="H33" s="3" t="inlineStr">
         <is>
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
       <c r="L33" s="3" t="n"/>
       <c r="M33" s="3" t="n"/>
       <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
+      <c r="O33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>RW; CN</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="n"/>
-      <c r="R33" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S33" s="3" t="n"/>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OBI_0000828</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t>RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W33" s="3" t="n"/>
@@ -2686,12 +2686,12 @@
           <t>An organisation that sells some product directly to users of that product.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
+      <c r="E34" s="2" t="n"/>
       <c r="F34" s="2" t="n"/>
       <c r="G34" s="2" t="n"/>
       <c r="H34" s="2" t="inlineStr">
@@ -2699,118 +2699,118 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="n"/>
       <c r="J34" s="2" t="n"/>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="2" t="n"/>
       <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="n"/>
+      <c r="O34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n">
+      <c r="R34" s="2" t="n"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>ADDICTO:0000435</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>tobacco company</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>A commercial organisation that is engaged in the growth, manufacture, preparation for sale, shipment, advertisement, or distribution of tobacco, or a tobacco-containing product, or is at least partly owned by such an organisation.</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>organisation</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>This excludes law firms acting for the TI. It also excludes organisations that are solely NRT manufacturers and e-cig manufacturers even though nicotine is derived from tobacco.</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>A commercial organisation that deals with tobacco in any part of the process from growing it to getting it to consumers, or is at least partly owned by such an organisation.</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="S34" s="2" t="n"/>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="n"/>
+      <c r="R35" s="4" t="n"/>
+      <c r="S35" s="4" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> RW; CN</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>ADDICTO:0000435</t>
-        </is>
-      </c>
-      <c r="B35" s="3" t="inlineStr">
-        <is>
-          <t>tobacco company</t>
-        </is>
-      </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>A commercial organisation that is engaged in the growth, manufacture, preparation for sale, shipment, advertisement, or distribution of tobacco, or a tobacco-containing product, or is at least partly owned by such an organisation.</t>
-        </is>
-      </c>
-      <c r="D35" s="3" t="inlineStr">
-        <is>
-          <t>A commercial organisation that deals with tobacco in any part of the process from growing it to getting it to consumers, or is at least partly owned by such an organisation.</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>organisation</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="n"/>
-      <c r="G35" s="3" t="n"/>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
+      <c r="T35" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="J35" s="3" t="n"/>
-      <c r="K35" s="3" t="n"/>
-      <c r="L35" s="3" t="n"/>
-      <c r="M35" s="3" t="n"/>
-      <c r="N35" s="3" t="n"/>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t>This excludes law firms acting for the TI. It also excludes NRT manufacturers and e-cig manufacturers even though nicotine is derived from tobacco.</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="n"/>
-      <c r="R35" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" s="3" t="n"/>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t>Pre-proposed</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> RW; CN</t>
-        </is>
-      </c>
-      <c r="W35" s="3" t="n"/>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>Discussed</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
           <t>An industry that is realised in the manufacture or sale of tobacco and tobacco-containing products.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
+      <c r="E36" s="2" t="n"/>
       <c r="F36" s="2" t="n"/>
       <c r="G36" s="2" t="n"/>
       <c r="H36" s="2" t="inlineStr">
@@ -2841,30 +2841,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>realizable entity</t>
-        </is>
-      </c>
+      <c r="I36" s="2" t="n"/>
       <c r="J36" s="2" t="n"/>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="2" t="n"/>
       <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P36" s="2" t="n"/>
+      <c r="O36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S36" s="2" t="n"/>
+      <c r="R36" s="2" t="n"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>realizable entity</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W36" s="2" t="n"/>
@@ -2895,12 +2895,12 @@
           <t>A facility that retails tobacco.</t>
         </is>
       </c>
-      <c r="D37" s="3" t="n"/>
-      <c r="E37" s="3" t="inlineStr">
+      <c r="D37" s="3" t="inlineStr">
         <is>
           <t>facility</t>
         </is>
       </c>
+      <c r="E37" s="3" t="n"/>
       <c r="F37" s="3" t="n"/>
       <c r="G37" s="3" t="n"/>
       <c r="H37" s="3" t="inlineStr">
@@ -2908,30 +2908,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="n"/>
       <c r="L37" s="3" t="n"/>
       <c r="M37" s="3" t="n"/>
       <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n"/>
+      <c r="O37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="n"/>
-      <c r="R37" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S37" s="3" t="n"/>
+      <c r="R37" s="3" t="n"/>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
@@ -2941,7 +2941,7 @@
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W37" s="3" t="n"/>
@@ -2962,12 +2962,12 @@
           <t xml:space="preserve">A retailer that sells tobacco products. </t>
         </is>
       </c>
-      <c r="D38" s="3" t="n"/>
-      <c r="E38" s="3" t="inlineStr">
+      <c r="D38" s="3" t="inlineStr">
         <is>
           <t>retailer</t>
         </is>
       </c>
+      <c r="E38" s="3" t="n"/>
       <c r="F38" s="3" t="n"/>
       <c r="G38" s="3" t="n"/>
       <c r="H38" s="3" t="inlineStr">
@@ -2975,30 +2975,30 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
       <c r="L38" s="3" t="n"/>
       <c r="M38" s="3" t="n"/>
       <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n"/>
+      <c r="O38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="n"/>
-      <c r="R38" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" s="3" t="n"/>
+      <c r="R38" s="3" t="n"/>
+      <c r="S38" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t>SC; JH; RW</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W38" s="3" t="n"/>
@@ -3031,14 +3031,10 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>A commercial organisation that deals with vaping devices or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
           <t>commercial organisation</t>
         </is>
       </c>
+      <c r="E39" s="2" t="n"/>
       <c r="F39" s="2" t="n"/>
       <c r="G39" s="2" t="n"/>
       <c r="H39" s="2" t="inlineStr">
@@ -3046,30 +3042,34 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="n"/>
-      <c r="O39" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P39" s="2" t="n"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>A commercial organisation that deals with vaping devices or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="S39" s="2" t="n"/>
+      <c r="R39" s="2" t="n"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>SC; JH</t>
+          <t>material entity</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -3079,7 +3079,7 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W39" s="2" t="n"/>

--- a/inputs/AddictO_Organisation_Defs.xlsx
+++ b/inputs/AddictO_Organisation_Defs.xlsx
@@ -39,7 +39,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ffffff"/>
+        <fgColor rgb="00ffe4b5"/>
       </patternFill>
     </fill>
     <fill>
@@ -49,7 +49,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ffe4b5"/>
+        <fgColor rgb="00ffffff"/>
       </patternFill>
     </fill>
     <fill>
@@ -615,7 +615,7 @@
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V2" s="2" t="n">
@@ -693,69 +693,69 @@
       <c r="W3" s="3" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>ADDICTO:0000411</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>alcohol industry</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>An industry that is realised in the manufacture and sale of alcoholic beverages.</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n"/>
-      <c r="F4" s="4" t="n"/>
-      <c r="G4" s="4" t="n"/>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="4" t="n"/>
-      <c r="L4" s="4" t="n"/>
-      <c r="M4" s="4" t="n"/>
-      <c r="N4" s="4" t="n"/>
-      <c r="O4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" s="4" t="n"/>
-      <c r="Q4" s="4" t="n"/>
-      <c r="R4" s="4" t="n"/>
-      <c r="S4" s="4" t="inlineStr">
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
+      <c r="G4" s="2" t="n"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n"/>
+      <c r="J4" s="2" t="n"/>
+      <c r="K4" s="2" t="n"/>
+      <c r="L4" s="2" t="n"/>
+      <c r="M4" s="2" t="n"/>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
+      <c r="Q4" s="2" t="n"/>
+      <c r="R4" s="2" t="n"/>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="T4" s="4" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="U4" s="4" t="inlineStr">
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V4" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" s="4" t="n"/>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -955,69 +955,69 @@
       <c r="W7" s="3" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0000415</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">cannabis industry </t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>An industry that is realised in the manufacture and sale of cannabis.</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
-      <c r="G8" s="2" t="n"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n"/>
-      <c r="J8" s="2" t="n"/>
-      <c r="K8" s="2" t="n"/>
-      <c r="L8" s="2" t="n"/>
-      <c r="M8" s="2" t="n"/>
-      <c r="N8" s="2" t="n"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="n"/>
-      <c r="Q8" s="2" t="n"/>
-      <c r="R8" s="2" t="n"/>
-      <c r="S8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="n"/>
+      <c r="F8" s="4" t="n"/>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+      <c r="M8" s="4" t="n"/>
+      <c r="N8" s="4" t="n"/>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="n"/>
+      <c r="Q8" s="4" t="n"/>
+      <c r="R8" s="4" t="n"/>
+      <c r="S8" s="4" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
+      <c r="T8" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="U8" s="2" t="inlineStr">
+      <c r="U8" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="n"/>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -1150,71 +1150,71 @@
       <c r="W10" s="3" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0001101</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">charity </t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">An organisation that raises and distributes funds for charitable purposes. </t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="2" t="n"/>
-      <c r="G11" s="2" t="n"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n"/>
-      <c r="J11" s="2" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="2" t="n"/>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="2" t="n">
+      <c r="E11" s="4" t="n"/>
+      <c r="F11" s="4" t="n"/>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+      <c r="M11" s="4" t="n"/>
+      <c r="N11" s="4" t="n"/>
+      <c r="O11" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="P11" s="4" t="inlineStr">
         <is>
           <t>RW; CN</t>
         </is>
       </c>
-      <c r="Q11" s="2" t="n"/>
-      <c r="R11" s="2" t="n"/>
-      <c r="S11" s="2" t="inlineStr">
+      <c r="Q11" s="4" t="n"/>
+      <c r="R11" s="4" t="n"/>
+      <c r="S11" s="4" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="T11" s="2" t="inlineStr">
+      <c r="T11" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="U11" s="2" t="inlineStr">
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="n"/>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V12" s="2" t="n">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V13" s="2" t="n">
@@ -1339,75 +1339,75 @@
       <c r="W13" s="2" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>ADDICTO:0000420</t>
         </is>
       </c>
-      <c r="B14" s="4" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>e-cigarette industry</t>
         </is>
       </c>
-      <c r="C14" s="4" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>An industry that is realised in the manufacture and sale of e-cigarettes, e-cigarette components and e-liquid.</t>
         </is>
       </c>
-      <c r="D14" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>E-Cig industry</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="inlineStr">
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n"/>
+      <c r="J14" s="2" t="n"/>
+      <c r="K14" s="2" t="n"/>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">I have added here promotion of - this sets industry apart from manufactureres of but also includes these types of company. </t>
         </is>
       </c>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n">
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P14" s="4" t="n"/>
-      <c r="Q14" s="4" t="n"/>
-      <c r="R14" s="4" t="n"/>
-      <c r="S14" s="4" t="inlineStr">
+      <c r="P14" s="2" t="n"/>
+      <c r="Q14" s="2" t="n"/>
+      <c r="R14" s="2" t="n"/>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="T14" s="4" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="U14" s="4" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V14" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" s="4" t="n"/>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -1615,69 +1615,69 @@
       <c r="W17" s="3" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0000424</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>gambling industry</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>An industry that is realised in the processes of facilitating and managing the wagering of money or valuables.</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E18" s="2" t="n"/>
-      <c r="F18" s="2" t="n"/>
-      <c r="G18" s="2" t="n"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n"/>
-      <c r="J18" s="2" t="n"/>
-      <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
-      <c r="M18" s="2" t="n"/>
-      <c r="N18" s="2" t="n"/>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="n"/>
-      <c r="Q18" s="2" t="n"/>
-      <c r="R18" s="2" t="n"/>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="n"/>
+      <c r="F18" s="4" t="n"/>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+      <c r="M18" s="4" t="n"/>
+      <c r="N18" s="4" t="n"/>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="n"/>
+      <c r="Q18" s="4" t="n"/>
+      <c r="R18" s="4" t="n"/>
+      <c r="S18" s="4" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T18" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="U18" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W18" s="2" t="n"/>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -1754,12 +1754,12 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>health-improvement organisation</t>
+          <t>health-improvement provider</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>An organisation that has as a function the production, distribution, or provision of goods or services intended to improve health or reduce ill-health.</t>
+          <t>An organisation that is engaged in the production, distribution, or provision of goods or services intended to improve health or reduce ill-health.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1799,7 +1799,7 @@
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V20" s="2" t="n">
@@ -1808,69 +1808,69 @@
       <c r="W20" s="2" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0001359</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">healthcare organisation </t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C21" s="4" t="inlineStr">
         <is>
           <t>An organisation that provides healthcare.</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="4" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="E21" s="2" t="n"/>
-      <c r="F21" s="2" t="n"/>
-      <c r="G21" s="2" t="n"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n"/>
-      <c r="J21" s="2" t="n"/>
-      <c r="K21" s="2" t="n"/>
-      <c r="L21" s="2" t="n"/>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="2" t="n"/>
-      <c r="O21" s="2" t="inlineStr">
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="P21" s="2" t="n"/>
-      <c r="Q21" s="2" t="n"/>
-      <c r="R21" s="2" t="n"/>
-      <c r="S21" s="2" t="inlineStr">
+      <c r="P21" s="4" t="n"/>
+      <c r="Q21" s="4" t="n"/>
+      <c r="R21" s="4" t="n"/>
+      <c r="S21" s="4" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="T21" s="2" t="inlineStr">
+      <c r="T21" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="U21" s="2" t="inlineStr">
+      <c r="U21" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" s="2" t="n"/>
+      <c r="V21" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" s="4" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -1948,142 +1948,142 @@
       <c r="W22" s="3" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>ADDICTO:0000428</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="C23" s="4" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>A realizable entity that inheres in a collection of organisations, people, equipment and resources and is realised in processes of production, distribution or service provision, and is characterised by a common purpose or set of related economic activities.</t>
         </is>
       </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n">
+      <c r="E23" s="2" t="n"/>
+      <c r="F23" s="2" t="n"/>
+      <c r="G23" s="2" t="n"/>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n"/>
+      <c r="J23" s="2" t="n"/>
+      <c r="K23" s="2" t="n"/>
+      <c r="L23" s="2" t="n"/>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P23" s="4" t="inlineStr">
+      <c r="P23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> RW; CN</t>
         </is>
       </c>
-      <c r="Q23" s="4" t="n"/>
-      <c r="R23" s="4" t="inlineStr">
+      <c r="Q23" s="2" t="n"/>
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>claude.ai</t>
         </is>
       </c>
-      <c r="S23" s="4" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
         <is>
           <t>JH; SC; RW</t>
         </is>
       </c>
-      <c r="T23" s="4" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="U23" s="4" t="inlineStr">
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V23" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" s="4" t="n"/>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>ADDICTO:0000429</t>
         </is>
       </c>
-      <c r="B24" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>marketing</t>
         </is>
       </c>
-      <c r="C24" s="4" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
         <is>
           <t>A process undertaken by an organisation with the aim of increasing use of a product or service.</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n">
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n"/>
+      <c r="J24" s="2" t="n"/>
+      <c r="K24" s="2" t="n"/>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P24" s="4" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> RW; CN</t>
         </is>
       </c>
-      <c r="Q24" s="4" t="n"/>
-      <c r="R24" s="4" t="n"/>
-      <c r="S24" s="4" t="inlineStr">
+      <c r="Q24" s="2" t="n"/>
+      <c r="R24" s="2" t="n"/>
+      <c r="S24" s="2" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="T24" s="4" t="inlineStr">
+      <c r="T24" s="2" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="U24" s="4" t="inlineStr">
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V24" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="n"/>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>A commercial organisation that is engaged in the manufacture, preparation for sale, shipment, advertisement, or distribution of  a pharmaceutical product or part of such a product, or is at least partly owned by such an organisation.</t>
+          <t>A commercial organisation that is engaged in the manufacture, preparation for sale, shipment, advertisement, or distribution of  a pharmaceutical product, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       <c r="M29" s="2" t="n"/>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>A commercial organisation that deals with pharmaceutical products or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
+          <t>A commercial organisation that deals with pharmaceutical products in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
       <c r="O29" s="2" t="b">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V29" s="2" t="n">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>recreational organisation</t>
+          <t>recreational consumer product organisation</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>An organisation that has as a function the production, distribution, or provision of goods or services intended for recreational use by consumers.</t>
+          <t>An organisation that is engaged in the production, distribution, or provision of goods or services intended for recreational use by consumers.</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2440,7 +2440,7 @@
       <c r="M30" s="2" t="n"/>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>An organisation that makes or provides products or services that people use for enjoyment, entertainment, or leisure activities.</t>
+          <t>An organisation that makes or provides consumer products or services that people use for enjoyment, entertainment, or leisure activities.</t>
         </is>
       </c>
       <c r="O30" s="2" t="b">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V30" s="2" t="n">
@@ -2466,138 +2466,138 @@
       <c r="W30" s="2" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0001102</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B31" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">regulatory agency </t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C31" s="4" t="inlineStr">
         <is>
           <t>An organization that has responsibility over or for the legislation (acts and regulations) for a given sector of the government.</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D31" s="4" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="E31" s="2" t="n"/>
-      <c r="F31" s="2" t="n"/>
-      <c r="G31" s="2" t="n"/>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n"/>
-      <c r="J31" s="2" t="n"/>
-      <c r="K31" s="2" t="n"/>
-      <c r="L31" s="2" t="n"/>
-      <c r="M31" s="2" t="n"/>
-      <c r="N31" s="2" t="n"/>
-      <c r="O31" s="2" t="n">
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P31" s="2" t="n"/>
-      <c r="Q31" s="2" t="n"/>
-      <c r="R31" s="2" t="inlineStr">
+      <c r="P31" s="4" t="n"/>
+      <c r="Q31" s="4" t="n"/>
+      <c r="R31" s="4" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OBI_0000450</t>
         </is>
       </c>
-      <c r="S31" s="2" t="inlineStr">
+      <c r="S31" s="4" t="inlineStr">
         <is>
           <t>SC; RW</t>
         </is>
       </c>
-      <c r="T31" s="2" t="inlineStr">
+      <c r="T31" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="U31" s="2" t="inlineStr">
+      <c r="U31" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W31" s="2" t="n"/>
+      <c r="V31" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0000880</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B32" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">research grant awarding body </t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C32" s="4" t="inlineStr">
         <is>
           <t>An organization that provides funding for research.</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D32" s="4" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E32" s="4" t="inlineStr">
         <is>
           <t>funder</t>
         </is>
       </c>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n"/>
-      <c r="J32" s="2" t="n"/>
-      <c r="K32" s="2" t="n"/>
-      <c r="L32" s="2" t="n"/>
-      <c r="M32" s="2" t="n"/>
-      <c r="N32" s="2" t="n"/>
-      <c r="O32" s="2" t="n">
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="2" t="n"/>
-      <c r="Q32" s="2" t="n"/>
-      <c r="R32" s="2" t="n"/>
-      <c r="S32" s="2" t="inlineStr">
+      <c r="P32" s="4" t="n"/>
+      <c r="Q32" s="4" t="n"/>
+      <c r="R32" s="4" t="n"/>
+      <c r="S32" s="4" t="inlineStr">
         <is>
           <t>SC; KS; RW</t>
         </is>
       </c>
-      <c r="T32" s="2" t="inlineStr">
+      <c r="T32" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="U32" s="2" t="inlineStr">
+      <c r="U32" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="n"/>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
@@ -2671,213 +2671,213 @@
       <c r="W33" s="3" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0000433</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>retailer</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>An organisation that sells some product directly to users of that product.</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n"/>
-      <c r="J34" s="2" t="n"/>
-      <c r="K34" s="2" t="n"/>
-      <c r="L34" s="2" t="n"/>
-      <c r="M34" s="2" t="n"/>
-      <c r="N34" s="2" t="n"/>
-      <c r="O34" s="2" t="n">
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P34" s="2" t="inlineStr">
+      <c r="P34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> RW; CN</t>
         </is>
       </c>
-      <c r="Q34" s="2" t="n"/>
-      <c r="R34" s="2" t="n"/>
-      <c r="S34" s="2" t="inlineStr">
+      <c r="Q34" s="4" t="n"/>
+      <c r="R34" s="4" t="n"/>
+      <c r="S34" s="4" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="T34" s="2" t="inlineStr">
+      <c r="T34" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="U34" s="2" t="inlineStr">
+      <c r="U34" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W34" s="2" t="n"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>ADDICTO:0000435</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>tobacco company</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that is engaged in the growth, manufacture, preparation for sale, shipment, advertisement, or distribution of tobacco, or a tobacco-containing product, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>organisation</t>
         </is>
       </c>
-      <c r="E35" s="4" t="n"/>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="E35" s="2" t="n"/>
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>This excludes law firms acting for the TI. It also excludes organisations that are solely NRT manufacturers and e-cig manufacturers even though nicotine is derived from tobacco.</t>
         </is>
       </c>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-      <c r="M35" s="4" t="n"/>
-      <c r="N35" s="4" t="inlineStr">
+      <c r="G35" s="2" t="n"/>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n"/>
+      <c r="J35" s="2" t="n"/>
+      <c r="K35" s="2" t="n"/>
+      <c r="L35" s="2" t="n"/>
+      <c r="M35" s="2" t="n"/>
+      <c r="N35" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that deals with tobacco in any part of the process from growing it to getting it to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="O35" s="4" t="n">
+      <c r="O35" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="P35" s="4" t="inlineStr">
+      <c r="P35" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve"> RW; CN</t>
         </is>
       </c>
-      <c r="Q35" s="4" t="n"/>
-      <c r="R35" s="4" t="n"/>
-      <c r="S35" s="4" t="inlineStr">
+      <c r="Q35" s="2" t="n"/>
+      <c r="R35" s="2" t="n"/>
+      <c r="S35" s="2" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="T35" s="4" t="inlineStr">
+      <c r="T35" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
-      <c r="U35" s="4" t="inlineStr">
+      <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
         </is>
       </c>
-      <c r="V35" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="n"/>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>ADDICTO:0000436</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>tobacco industry</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>An industry that is realised in the manufacture or sale of tobacco and tobacco-containing products.</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D36" s="4" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n"/>
-      <c r="F36" s="2" t="n"/>
-      <c r="G36" s="2" t="n"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>Organisation</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n"/>
-      <c r="J36" s="2" t="n"/>
-      <c r="K36" s="2" t="n"/>
-      <c r="L36" s="2" t="n"/>
-      <c r="M36" s="2" t="n"/>
-      <c r="N36" s="2" t="n"/>
-      <c r="O36" s="2" t="n">
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Organisation</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+      <c r="M36" s="4" t="n"/>
+      <c r="N36" s="4" t="n"/>
+      <c r="O36" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="P36" s="2" t="inlineStr">
+      <c r="P36" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve"> RW; CN</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="n"/>
-      <c r="R36" s="2" t="n"/>
-      <c r="S36" s="2" t="inlineStr">
+      <c r="Q36" s="4" t="n"/>
+      <c r="R36" s="4" t="n"/>
+      <c r="S36" s="4" t="inlineStr">
         <is>
           <t>SC; JH; RW</t>
         </is>
       </c>
-      <c r="T36" s="2" t="inlineStr">
+      <c r="T36" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
-      <c r="U36" s="2" t="inlineStr">
+      <c r="U36" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W36" s="2" t="n"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
@@ -3074,7 +3074,7 @@
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>Proposed</t>
+          <t>Discussed</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">

--- a/inputs/AddictO_Organisation_Defs.xlsx
+++ b/inputs/AddictO_Organisation_Defs.xlsx
@@ -493,57 +493,57 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Cross reference</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Curator note</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>E-CigO</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>To be reviewed by</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Examples of usage</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Definition source</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Curator</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Informal definition</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>BFO entity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
           <t>REL 'has role'</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>REL 'has part'</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Cross reference</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Curator note</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Informal definition</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>E-CigO</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>To be reviewed by</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Examples of usage</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Definition source</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Curator</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>BFO entity</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
@@ -594,25 +594,25 @@
       <c r="I2" s="2" t="n"/>
       <c r="J2" s="2" t="n"/>
       <c r="K2" s="2" t="n"/>
-      <c r="L2" s="2" t="n"/>
+      <c r="L2" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M2" s="2" t="n"/>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
+      <c r="P2" s="2" t="n"/>
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that deals with nicotine products or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="O2" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="n"/>
-      <c r="Q2" s="2" t="n"/>
-      <c r="R2" s="2" t="n"/>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="S2" s="2" t="n"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="T2" s="2" t="n"/>
       <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -659,27 +659,27 @@
       <c r="I3" s="3" t="n"/>
       <c r="J3" s="3" t="n"/>
       <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M3" s="3" t="n"/>
       <c r="N3" s="3" t="n"/>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n"/>
+      <c r="O3" s="3" t="n"/>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="n"/>
-      <c r="R3" s="3" t="n"/>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
+      <c r="R3" s="3" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S3" s="3" t="n"/>
+      <c r="T3" s="3" t="n"/>
       <c r="U3" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -724,27 +724,27 @@
       <c r="I4" s="2" t="n"/>
       <c r="J4" s="2" t="n"/>
       <c r="K4" s="2" t="n"/>
-      <c r="L4" s="2" t="n"/>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q4" s="2" t="n"/>
-      <c r="R4" s="2" t="n"/>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
+      <c r="S4" s="2" t="n"/>
+      <c r="T4" s="2" t="n"/>
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -789,27 +789,27 @@
       <c r="I5" s="3" t="n"/>
       <c r="J5" s="3" t="n"/>
       <c r="K5" s="3" t="n"/>
-      <c r="L5" s="3" t="n"/>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M5" s="3" t="n"/>
       <c r="N5" s="3" t="n"/>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+      <c r="O5" s="3" t="n"/>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="n"/>
-      <c r="R5" s="3" t="n"/>
-      <c r="S5" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="T5" s="3" t="inlineStr">
+      <c r="R5" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Role </t>
         </is>
       </c>
+      <c r="S5" s="3" t="n"/>
+      <c r="T5" s="3" t="n"/>
       <c r="U5" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -858,25 +858,25 @@
       <c r="I6" s="3" t="n"/>
       <c r="J6" s="3" t="n"/>
       <c r="K6" s="3" t="n"/>
-      <c r="L6" s="3" t="n"/>
+      <c r="L6" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M6" s="3" t="n"/>
       <c r="N6" s="3" t="n"/>
-      <c r="O6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="3" t="n"/>
+      <c r="O6" s="3" t="n"/>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="n"/>
-      <c r="R6" s="3" t="n"/>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="inlineStr">
+      <c r="R6" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Role </t>
         </is>
       </c>
+      <c r="S6" s="3" t="n"/>
+      <c r="T6" s="3" t="n"/>
       <c r="U6" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -921,27 +921,27 @@
       <c r="I7" s="3" t="n"/>
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="n"/>
-      <c r="L7" s="3" t="n"/>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M7" s="3" t="n"/>
       <c r="N7" s="3" t="n"/>
-      <c r="O7" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n"/>
+      <c r="O7" s="3" t="n"/>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>SC; JH; KS</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="n"/>
-      <c r="R7" s="3" t="n"/>
-      <c r="S7" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH; KS</t>
-        </is>
-      </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="R7" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Role </t>
         </is>
       </c>
+      <c r="S7" s="3" t="n"/>
+      <c r="T7" s="3" t="n"/>
       <c r="U7" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -986,27 +986,27 @@
       <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="n"/>
       <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M8" s="4" t="n"/>
       <c r="N8" s="4" t="n"/>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" s="4" t="n"/>
+      <c r="O8" s="4" t="n"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q8" s="4" t="n"/>
-      <c r="R8" s="4" t="n"/>
-      <c r="S8" s="4" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T8" s="4" t="inlineStr">
+      <c r="R8" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
+      <c r="S8" s="4" t="n"/>
+      <c r="T8" s="4" t="n"/>
       <c r="U8" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -1051,27 +1051,27 @@
       <c r="I9" s="3" t="n"/>
       <c r="J9" s="3" t="n"/>
       <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M9" s="3" t="n"/>
       <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+      <c r="O9" s="3" t="n"/>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="n"/>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="inlineStr">
+      <c r="R9" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Role </t>
         </is>
       </c>
+      <c r="S9" s="3" t="n"/>
+      <c r="T9" s="3" t="n"/>
       <c r="U9" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1116,27 +1116,27 @@
       <c r="I10" s="3" t="n"/>
       <c r="J10" s="3" t="n"/>
       <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M10" s="3" t="n"/>
       <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
+      <c r="O10" s="3" t="n"/>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="n"/>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="inlineStr">
+      <c r="R10" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Role </t>
         </is>
       </c>
+      <c r="S10" s="3" t="n"/>
+      <c r="T10" s="3" t="n"/>
       <c r="U10" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1181,29 +1181,29 @@
       <c r="I11" s="4" t="n"/>
       <c r="J11" s="4" t="n"/>
       <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
+      <c r="L11" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>RW; CN</t>
+        </is>
+      </c>
       <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O11" s="4" t="n"/>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n"/>
-      <c r="R11" s="4" t="n"/>
-      <c r="S11" s="4" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T11" s="4" t="inlineStr">
+      <c r="R11" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S11" s="4" t="n"/>
+      <c r="T11" s="4" t="n"/>
       <c r="U11" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -1248,25 +1248,25 @@
       <c r="I12" s="2" t="n"/>
       <c r="J12" s="2" t="n"/>
       <c r="K12" s="2" t="n"/>
-      <c r="L12" s="2" t="n"/>
+      <c r="L12" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="N12" s="2" t="n"/>
+      <c r="O12" s="2" t="n"/>
+      <c r="P12" s="2" t="n"/>
+      <c r="Q12" s="2" t="inlineStr">
         <is>
           <t>An organisation whose main goal is making money by selling products or services.</t>
         </is>
       </c>
-      <c r="O12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P12" s="2" t="n"/>
-      <c r="Q12" s="2" t="n"/>
-      <c r="R12" s="2" t="n"/>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="S12" s="2" t="n"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="T12" s="2" t="n"/>
       <c r="U12" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -1309,25 +1309,25 @@
       <c r="I13" s="2" t="n"/>
       <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="n"/>
+      <c r="L13" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="n"/>
+      <c r="O13" s="2" t="n"/>
+      <c r="P13" s="2" t="n"/>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that deals with e-cigarettes or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="O13" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P13" s="2" t="n"/>
-      <c r="Q13" s="2" t="n"/>
-      <c r="R13" s="2" t="n"/>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="S13" s="2" t="n"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="T13" s="2" t="n"/>
       <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -1373,30 +1373,30 @@
       </c>
       <c r="I14" s="2" t="n"/>
       <c r="J14" s="2" t="n"/>
-      <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="n"/>
-      <c r="M14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">I have added here promotion of - this sets industry apart from manufactureres of but also includes these types of company. </t>
         </is>
       </c>
+      <c r="L14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" s="2" t="n"/>
       <c r="N14" s="2" t="n"/>
-      <c r="O14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P14" s="2" t="n"/>
+      <c r="O14" s="2" t="n"/>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q14" s="2" t="n"/>
-      <c r="R14" s="2" t="n"/>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
+      <c r="S14" s="2" t="n"/>
+      <c r="T14" s="2" t="n"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -1445,29 +1445,29 @@
       <c r="I15" s="3" t="n"/>
       <c r="J15" s="3" t="n"/>
       <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
-      <c r="M15" s="3" t="n"/>
+      <c r="L15" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O15" s="3" t="n"/>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH</t>
         </is>
       </c>
       <c r="Q15" s="3" t="n"/>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH</t>
-        </is>
-      </c>
-      <c r="T15" s="3" t="inlineStr">
+      <c r="R15" s="3" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
+      <c r="S15" s="3" t="n"/>
+      <c r="T15" s="3" t="n"/>
       <c r="U15" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1512,29 +1512,29 @@
       <c r="I16" s="3" t="n"/>
       <c r="J16" s="3" t="n"/>
       <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
-      <c r="M16" s="3" t="n"/>
+      <c r="L16" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O16" s="3" t="n"/>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH</t>
         </is>
       </c>
       <c r="Q16" s="3" t="n"/>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="inlineStr">
+      <c r="R16" s="3" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
+      <c r="S16" s="3" t="n"/>
+      <c r="T16" s="3" t="n"/>
       <c r="U16" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1579,29 +1579,29 @@
       <c r="I17" s="3" t="n"/>
       <c r="J17" s="3" t="n"/>
       <c r="K17" s="3" t="n"/>
-      <c r="L17" s="3" t="n"/>
-      <c r="M17" s="3" t="n"/>
+      <c r="L17" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N17" s="3" t="n"/>
-      <c r="O17" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O17" s="3" t="n"/>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH</t>
         </is>
       </c>
       <c r="Q17" s="3" t="n"/>
-      <c r="R17" s="3" t="n"/>
-      <c r="S17" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH</t>
-        </is>
-      </c>
-      <c r="T17" s="3" t="inlineStr">
+      <c r="R17" s="3" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
+      <c r="S17" s="3" t="n"/>
+      <c r="T17" s="3" t="n"/>
       <c r="U17" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1646,27 +1646,27 @@
       <c r="I18" s="4" t="n"/>
       <c r="J18" s="4" t="n"/>
       <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M18" s="4" t="n"/>
       <c r="N18" s="4" t="n"/>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P18" s="4" t="n"/>
+      <c r="O18" s="4" t="n"/>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q18" s="4" t="n"/>
-      <c r="R18" s="4" t="n"/>
-      <c r="S18" s="4" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T18" s="4" t="inlineStr">
+      <c r="R18" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
+      <c r="S18" s="4" t="n"/>
+      <c r="T18" s="4" t="n"/>
       <c r="U18" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -1715,25 +1715,25 @@
       <c r="I19" s="3" t="n"/>
       <c r="J19" s="3" t="n"/>
       <c r="K19" s="3" t="n"/>
-      <c r="L19" s="3" t="n"/>
+      <c r="L19" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M19" s="3" t="n"/>
       <c r="N19" s="3" t="n"/>
-      <c r="O19" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" s="3" t="n"/>
+      <c r="O19" s="3" t="n"/>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="n"/>
-      <c r="R19" s="3" t="n"/>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-      <c r="T19" s="3" t="inlineStr">
+      <c r="R19" s="3" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
+      <c r="S19" s="3" t="n"/>
+      <c r="T19" s="3" t="n"/>
       <c r="U19" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1778,25 +1778,25 @@
       <c r="I20" s="2" t="n"/>
       <c r="J20" s="2" t="n"/>
       <c r="K20" s="2" t="n"/>
-      <c r="L20" s="2" t="n"/>
+      <c r="L20" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M20" s="2" t="n"/>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="n"/>
+      <c r="P20" s="2" t="n"/>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>An organisation that provides products or services that are used for purposes of improving health or reducing ill-health.</t>
         </is>
       </c>
-      <c r="O20" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P20" s="2" t="n"/>
-      <c r="Q20" s="2" t="n"/>
-      <c r="R20" s="2" t="n"/>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="S20" s="2" t="n"/>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="T20" s="2" t="n"/>
       <c r="U20" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -1839,27 +1839,27 @@
       <c r="I21" s="4" t="n"/>
       <c r="J21" s="4" t="n"/>
       <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="M21" s="4" t="n"/>
       <c r="N21" s="4" t="n"/>
-      <c r="O21" s="4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
       <c r="Q21" s="4" t="n"/>
-      <c r="R21" s="4" t="n"/>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="inlineStr">
+      <c r="R21" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S21" s="4" t="n"/>
+      <c r="T21" s="4" t="n"/>
       <c r="U21" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -1912,29 +1912,29 @@
       <c r="I22" s="3" t="n"/>
       <c r="J22" s="3" t="n"/>
       <c r="K22" s="3" t="n"/>
-      <c r="L22" s="3" t="n"/>
-      <c r="M22" s="3" t="n"/>
+      <c r="L22" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="n"/>
-      <c r="O22" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O22" s="3" t="n"/>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t>RW</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="Q22" s="3" t="n"/>
-      <c r="R22" s="3" t="n"/>
-      <c r="S22" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="T22" s="3" t="inlineStr">
+      <c r="R22" s="3" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
+      <c r="S22" s="3" t="n"/>
+      <c r="T22" s="3" t="n"/>
       <c r="U22" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -1979,33 +1979,33 @@
       <c r="I23" s="2" t="n"/>
       <c r="J23" s="2" t="n"/>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="n"/>
-      <c r="M23" s="2" t="n"/>
+      <c r="L23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="n"/>
-      <c r="O23" s="2" t="n">
-        <v>1</v>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>claude.ai</t>
+        </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>JH; SC; RW</t>
         </is>
       </c>
       <c r="Q23" s="2" t="n"/>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>claude.ai</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>JH; SC; RW</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
           <t>realizable entity</t>
         </is>
       </c>
+      <c r="S23" s="2" t="n"/>
+      <c r="T23" s="2" t="n"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -2050,29 +2050,29 @@
       <c r="I24" s="2" t="n"/>
       <c r="J24" s="2" t="n"/>
       <c r="K24" s="2" t="n"/>
-      <c r="L24" s="2" t="n"/>
-      <c r="M24" s="2" t="n"/>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="n"/>
-      <c r="O24" s="2" t="n">
-        <v>1</v>
-      </c>
+      <c r="O24" s="2" t="n"/>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q24" s="2" t="n"/>
-      <c r="R24" s="2" t="n"/>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
+      <c r="S24" s="2" t="n"/>
+      <c r="T24" s="2" t="n"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -2117,25 +2117,25 @@
       <c r="I25" s="3" t="n"/>
       <c r="J25" s="3" t="n"/>
       <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+      <c r="L25" s="3" t="n">
+        <v>1</v>
+      </c>
       <c r="M25" s="3" t="n"/>
       <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P25" s="3" t="n"/>
+      <c r="O25" s="3" t="n"/>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="n"/>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
+      <c r="R25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Role </t>
         </is>
       </c>
+      <c r="S25" s="3" t="n"/>
+      <c r="T25" s="3" t="n"/>
       <c r="U25" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -2180,31 +2180,31 @@
       <c r="I26" s="3" t="n"/>
       <c r="J26" s="3" t="n"/>
       <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
       <c r="M26" s="3" t="n"/>
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>true</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n"/>
+          <t>http://purl.obolibrary.org/obo/GSSO_004615</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="n"/>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/GSSO_004615</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S26" s="3" t="n"/>
+      <c r="T26" s="3" t="n"/>
       <c r="U26" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -2248,25 +2248,25 @@
           <t>Organisation</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>The definition from OBI has been slightly changed to refer to 'material entity' rather than 'continuant entity'</t>
         </is>
       </c>
-      <c r="O27" t="n">
+      <c r="L27" t="n">
         <v>1</v>
       </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>OBI:0000245</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>RW</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
-        <is>
-          <t>OBI:0000245</t>
-        </is>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>RW</t>
-        </is>
-      </c>
-      <c r="T27" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
@@ -2314,22 +2314,22 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="5" t="n"/>
       <c r="K28" s="5" t="n"/>
-      <c r="L28" s="5" t="n"/>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
       <c r="M28" s="5" t="n"/>
       <c r="N28" s="5" t="n"/>
-      <c r="O28" s="5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="inlineStr">
+        <is>
+          <t>JH; RW</t>
+        </is>
+      </c>
       <c r="Q28" s="5" t="n"/>
       <c r="R28" s="5" t="n"/>
-      <c r="S28" s="5" t="inlineStr">
-        <is>
-          <t>JH; RW</t>
-        </is>
-      </c>
+      <c r="S28" s="5" t="n"/>
       <c r="T28" s="5" t="n"/>
       <c r="U28" s="5" t="inlineStr">
         <is>
@@ -2375,25 +2375,25 @@
       <c r="I29" s="2" t="n"/>
       <c r="J29" s="2" t="n"/>
       <c r="K29" s="2" t="n"/>
-      <c r="L29" s="2" t="n"/>
+      <c r="L29" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M29" s="2" t="n"/>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="N29" s="2" t="n"/>
+      <c r="O29" s="2" t="n"/>
+      <c r="P29" s="2" t="n"/>
+      <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that deals with pharmaceutical products in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="O29" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" s="2" t="n"/>
-      <c r="Q29" s="2" t="n"/>
-      <c r="R29" s="2" t="n"/>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="S29" s="2" t="n"/>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="T29" s="2" t="n"/>
       <c r="U29" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -2436,25 +2436,25 @@
       <c r="I30" s="2" t="n"/>
       <c r="J30" s="2" t="n"/>
       <c r="K30" s="2" t="n"/>
-      <c r="L30" s="2" t="n"/>
+      <c r="L30" s="2" t="b">
+        <v>1</v>
+      </c>
       <c r="M30" s="2" t="n"/>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="N30" s="2" t="n"/>
+      <c r="O30" s="2" t="n"/>
+      <c r="P30" s="2" t="n"/>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>An organisation that makes or provides consumer products or services that people use for enjoyment, entertainment, or leisure activities.</t>
         </is>
       </c>
-      <c r="O30" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="P30" s="2" t="n"/>
-      <c r="Q30" s="2" t="n"/>
-      <c r="R30" s="2" t="n"/>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>material entity</t>
+        </is>
+      </c>
       <c r="S30" s="2" t="n"/>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>material entity</t>
-        </is>
-      </c>
+      <c r="T30" s="2" t="n"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -2497,29 +2497,29 @@
       <c r="I31" s="4" t="n"/>
       <c r="J31" s="4" t="n"/>
       <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
+      <c r="L31" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M31" s="4" t="n"/>
       <c r="N31" s="4" t="n"/>
-      <c r="O31" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P31" s="4" t="n"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OBI_0000450</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>SC; RW</t>
+        </is>
+      </c>
       <c r="Q31" s="4" t="n"/>
       <c r="R31" s="4" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OBI_0000450</t>
-        </is>
-      </c>
-      <c r="S31" s="4" t="inlineStr">
-        <is>
-          <t>SC; RW</t>
-        </is>
-      </c>
-      <c r="T31" s="4" t="inlineStr">
-        <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S31" s="4" t="n"/>
+      <c r="T31" s="4" t="n"/>
       <c r="U31" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -2568,25 +2568,25 @@
       <c r="I32" s="4" t="n"/>
       <c r="J32" s="4" t="n"/>
       <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
+      <c r="L32" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="M32" s="4" t="n"/>
       <c r="N32" s="4" t="n"/>
-      <c r="O32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>SC; KS; RW</t>
+        </is>
+      </c>
       <c r="Q32" s="4" t="n"/>
-      <c r="R32" s="4" t="n"/>
-      <c r="S32" s="4" t="inlineStr">
-        <is>
-          <t>SC; KS; RW</t>
-        </is>
-      </c>
-      <c r="T32" s="4" t="inlineStr">
+      <c r="R32" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S32" s="4" t="n"/>
+      <c r="T32" s="4" t="n"/>
       <c r="U32" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -2631,33 +2631,33 @@
       <c r="I33" s="3" t="n"/>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
-      <c r="M33" s="3" t="n"/>
+      <c r="L33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>RW; CN</t>
+        </is>
+      </c>
       <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n">
-        <v>1</v>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OBI_0000828</t>
+        </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t>RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q33" s="3" t="n"/>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OBI_0000828</t>
-        </is>
-      </c>
-      <c r="S33" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T33" s="3" t="inlineStr">
-        <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S33" s="3" t="n"/>
+      <c r="T33" s="3" t="n"/>
       <c r="U33" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -2702,29 +2702,29 @@
       <c r="I34" s="4" t="n"/>
       <c r="J34" s="4" t="n"/>
       <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-      <c r="M34" s="4" t="n"/>
+      <c r="L34" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N34" s="4" t="n"/>
-      <c r="O34" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O34" s="4" t="n"/>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n"/>
-      <c r="R34" s="4" t="n"/>
-      <c r="S34" s="4" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T34" s="4" t="inlineStr">
+      <c r="R34" s="4" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S34" s="4" t="n"/>
+      <c r="T34" s="4" t="n"/>
       <c r="U34" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -2773,33 +2773,33 @@
       <c r="I35" s="2" t="n"/>
       <c r="J35" s="2" t="n"/>
       <c r="K35" s="2" t="n"/>
-      <c r="L35" s="2" t="n"/>
-      <c r="M35" s="2" t="n"/>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="L35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="n"/>
+      <c r="O35" s="2" t="n"/>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH; RW</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that deals with tobacco in any part of the process from growing it to getting it to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="O35" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> RW; CN</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="n"/>
-      <c r="R35" s="2" t="n"/>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
+      <c r="R35" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S35" s="2" t="n"/>
+      <c r="T35" s="2" t="n"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
@@ -2844,29 +2844,29 @@
       <c r="I36" s="4" t="n"/>
       <c r="J36" s="4" t="n"/>
       <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-      <c r="M36" s="4" t="n"/>
+      <c r="L36" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N36" s="4" t="n"/>
-      <c r="O36" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="O36" s="4" t="n"/>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n"/>
-      <c r="R36" s="4" t="n"/>
-      <c r="S36" s="4" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T36" s="4" t="inlineStr">
+      <c r="R36" s="4" t="inlineStr">
         <is>
           <t>realizable entity</t>
         </is>
       </c>
+      <c r="S36" s="4" t="n"/>
+      <c r="T36" s="4" t="n"/>
       <c r="U36" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
@@ -2911,29 +2911,29 @@
       <c r="I37" s="3" t="n"/>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="n"/>
-      <c r="L37" s="3" t="n"/>
-      <c r="M37" s="3" t="n"/>
+      <c r="L37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N37" s="3" t="n"/>
-      <c r="O37" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O37" s="3" t="n"/>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q37" s="3" t="n"/>
-      <c r="R37" s="3" t="n"/>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T37" s="3" t="inlineStr">
+      <c r="R37" s="3" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S37" s="3" t="n"/>
+      <c r="T37" s="3" t="n"/>
       <c r="U37" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -2978,29 +2978,29 @@
       <c r="I38" s="3" t="n"/>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="n"/>
-      <c r="L38" s="3" t="n"/>
-      <c r="M38" s="3" t="n"/>
+      <c r="L38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="n"/>
-      <c r="O38" s="3" t="n">
-        <v>1</v>
-      </c>
+      <c r="O38" s="3" t="n"/>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve"> RW; CN</t>
+          <t>SC; JH; RW</t>
         </is>
       </c>
       <c r="Q38" s="3" t="n"/>
-      <c r="R38" s="3" t="n"/>
-      <c r="S38" s="3" t="inlineStr">
-        <is>
-          <t>SC; JH; RW</t>
-        </is>
-      </c>
-      <c r="T38" s="3" t="inlineStr">
+      <c r="R38" s="3" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S38" s="3" t="n"/>
+      <c r="T38" s="3" t="n"/>
       <c r="U38" s="3" t="inlineStr">
         <is>
           <t>Pre-proposed</t>
@@ -3045,33 +3045,33 @@
       <c r="I39" s="2" t="n"/>
       <c r="J39" s="2" t="n"/>
       <c r="K39" s="2" t="n"/>
-      <c r="L39" s="2" t="n"/>
-      <c r="M39" s="2" t="n"/>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="L39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> RW; CN</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="n"/>
+      <c r="O39" s="2" t="n"/>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SC; JH</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr">
         <is>
           <t>A commercial organisation that deals with vaping devices or their parts in any part of the process from manufacturing them to getting them to consumers, or is at least partly owned by such an organisation.</t>
         </is>
       </c>
-      <c r="O39" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="P39" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> RW; CN</t>
-        </is>
-      </c>
-      <c r="Q39" s="2" t="n"/>
-      <c r="R39" s="2" t="n"/>
-      <c r="S39" s="2" t="inlineStr">
-        <is>
-          <t>SC; JH</t>
-        </is>
-      </c>
-      <c r="T39" s="2" t="inlineStr">
+      <c r="R39" s="2" t="inlineStr">
         <is>
           <t>material entity</t>
         </is>
       </c>
+      <c r="S39" s="2" t="n"/>
+      <c r="T39" s="2" t="n"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
           <t>Discussed</t>
